--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20232.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,43 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>MENDOZA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>GERSON</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
+    <t>ERIK OMAR</t>
   </si>
 </sst>
 </file>
@@ -662,16 +632,19 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>31</v>
       </c>
-      <c r="E2">
-        <v>31</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -685,16 +658,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -708,16 +684,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>76.67</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -731,16 +710,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H5">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -796,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -822,16 +804,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -848,16 +830,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>73.33</v>
+        <v>76.67</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -874,16 +856,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>39.13</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -925,7 +907,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920183</v>
+        <v>22330051920192</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -934,7 +916,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -944,98 +926,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920188</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920413</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920184</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920180</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20232.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
   </si>
 </sst>
 </file>
@@ -787,7 +778,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -804,16 +795,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -830,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>76.67</v>
+        <v>83.33</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -856,16 +847,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>95.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -905,29 +896,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920192</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
